--- a/资料/规则与例句数据库/转写辨析案例.xlsx
+++ b/资料/规则与例句数据库/转写辨析案例.xlsx
@@ -60,8 +60,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RevisionCases" displayName="RevisionCases" ref="A1:G17" totalsRowShown="0">
-  <autoFilter ref="A1:G17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RevisionCases" displayName="RevisionCases" ref="A1:G37" totalsRowShown="0">
+  <autoFilter ref="A1:G37"/>
   <tableColumns count="7">
     <tableColumn id="1" name="编号"/>
     <tableColumn id="2" name="原句／问题"/>
@@ -716,6 +716,746 @@
         </is>
       </c>
     </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" t="inlineStr" s="2">
+        <is>
+          <t>小满-M001</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr" s="2">
+        <is>
+          <t>路口红灯一直闪</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr" s="2">
+        <is>
+          <t>需要呈现交通灯的位置、朝向与闪动时</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr" s="2">
+        <is>
+          <t>词条选择与画面朝向；批注不能当作已修改正文</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr" s="2">
+        <is>
+          <t>R06 R02</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr" s="2">
+        <is>
+          <t>小美满</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr" s="2">
+        <is>
+          <t>查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" t="inlineStr" s="3">
+        <is>
+          <t>小满-M002</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr" s="3">
+        <is>
+          <t>眨眼的小太阳</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr" s="3">
+        <is>
+          <t>拟人意象需要把前一个对象与后一个动作连起来时</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr" s="3">
+        <is>
+          <t>太阳打完后承接眨眼动作</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr" s="3">
+        <is>
+          <t>R09</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr" s="3">
+        <is>
+          <t>小美满</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr" s="3">
+        <is>
+          <t>查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" t="inlineStr" s="2">
+        <is>
+          <t>小满-M003</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr" s="2">
+        <is>
+          <t>捏成棉花糖</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr" s="2">
+        <is>
+          <t>歌词快，怀疑动作太多而想删词时</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr" s="2">
+        <is>
+          <t>删词与左右手安排有不同意见</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr" s="2">
+        <is>
+          <t>R14</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr" s="2">
+        <is>
+          <t>小美满</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr" s="2">
+        <is>
+          <t>查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" t="inlineStr" s="3">
+        <is>
+          <t>小满-M004</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr" s="3">
+        <is>
+          <t>揉揉疲惫的眼睛</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr" s="3">
+        <is>
+          <t>一句本身描述可直接做出的具体动作时</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr" s="3">
+        <is>
+          <t>直接揉眼动作与分词转写的比较</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr" s="3">
+        <is>
+          <t>R09</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr" s="3">
+        <is>
+          <t>小美满</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr" s="3">
+        <is>
+          <t>查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" t="inlineStr" s="2">
+        <is>
+          <t>小满-M005</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr" s="2">
+        <is>
+          <t>床单洒满阳光</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr" s="2">
+        <is>
+          <t>想表现阳光与床的空间关系时</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr" s="2">
+        <is>
+          <t>左右手分工如何呈现一个画面</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr" s="2">
+        <is>
+          <t>R06 R09</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr" s="2">
+        <is>
+          <t>小美满</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr" s="2">
+        <is>
+          <t>查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" t="inlineStr" s="3">
+        <is>
+          <t>小满-M006</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr" s="3">
+        <is>
+          <t>夜里看月亮</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr" s="3">
+        <is>
+          <t>已有词序或连接词打起来不顺时</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr" s="3">
+        <is>
+          <t>画面顺序与去掉连接词的考虑</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr" s="3">
+        <is>
+          <t>R01 R14</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr" s="3">
+        <is>
+          <t>小美满</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr" s="3">
+        <is>
+          <t>查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" t="inlineStr" s="2">
+        <is>
+          <t>小满-M007</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr" s="2">
+        <is>
+          <t>留一扇天窗</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr" s="2">
+        <is>
+          <t>文字词名正确但配图可能指向别的对象时</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr" s="2">
+        <is>
+          <t>窗户与门的图片是否匹配</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr" s="2">
+        <is>
+          <t>小美满</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr" s="2">
+        <is>
+          <t>查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" t="inlineStr" s="3">
+        <is>
+          <t>小满-M008</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr" s="3">
+        <is>
+          <t>难题加点重量</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr" s="3">
+        <is>
+          <t>抽象负担想借身体位置具体呈现时</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr" s="3">
+        <is>
+          <t>施压、重担与责任的动作选择</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr" s="3">
+        <is>
+          <t>R09</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr" s="3">
+        <is>
+          <t>小美满</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr" s="3">
+        <is>
+          <t>查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" t="inlineStr" s="2">
+        <is>
+          <t>暮色-M001</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr" s="2">
+        <is>
+          <t>仍然选择留下</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr" s="2">
+        <is>
+          <t>否定愿意离别，或考虑查已有否定词条时</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr" s="2">
+        <is>
+          <t>离别／愿意／不与不愿意词条</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr" s="2">
+        <is>
+          <t>R03 R10</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr" s="2">
+        <is>
+          <t>暮色回响</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr" s="2">
+        <is>
+          <t>查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" t="inlineStr" s="3">
+        <is>
+          <t>暮色-M002</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr" s="3">
+        <is>
+          <t>借你给我回答</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr" s="3">
+        <is>
+          <t>多个人物之间转述或传递信息时</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr" s="3">
+        <is>
+          <t>他、你、我的指向链与疑问表情</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr" s="3">
+        <is>
+          <t>R06 R04</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr" s="3">
+        <is>
+          <t>暮色回响</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr" s="3">
+        <is>
+          <t>查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" t="inlineStr" s="2">
+        <is>
+          <t>蝶-M001</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr" s="2">
+        <is>
+          <t>去探索这个世界它变化万千</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr" s="2">
+        <is>
+          <t>原句含定语从句，修饰层层嵌套时</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr" s="2">
+        <is>
+          <t>拆成短句；再次交代陈述对象</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr" s="2">
+        <is>
+          <t>R13 R02</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr" s="2">
+        <is>
+          <t>Two Oruguitas</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr" s="2">
+        <is>
+          <t>查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" t="inlineStr" s="3">
+        <is>
+          <t>蝶-M002</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr" s="3">
+        <is>
+          <t>别再苦苦相依</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr" s="3">
+        <is>
+          <t>想表达紧紧、苦苦等程度，又不希望不断增添词时</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr" s="3">
+        <is>
+          <t>动作延长与非手控如何配合</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr" s="3">
+        <is>
+          <t>R02 R08 R03</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr" s="3">
+        <is>
+          <t>Two Oruguitas</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr" s="3">
+        <is>
+          <t>查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" t="inlineStr" s="2">
+        <is>
+          <t>蝶-M003</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr" s="2">
+        <is>
+          <t>彼此的避风港与身体变化</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr" s="2">
+        <is>
+          <t>抽象意象与具体画面之间难以取舍时</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr" s="2">
+        <is>
+          <t>歌词版本、对仗与化茧成蝶主题的综合取舍</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr" s="2">
+        <is>
+          <t>R09 R11</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr" s="2">
+        <is>
+          <t>Two Oruguitas</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr" s="2">
+        <is>
+          <t>查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" t="inlineStr" s="3">
+        <is>
+          <t>蝶-M004</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr" s="3">
+        <is>
+          <t>飞翔成长与蝴蝶类标记</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr" s="3">
+        <is>
+          <t>已经交代主体，后续动作考虑用类标记承接时</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr" s="3">
+        <is>
+          <t>主体已明确后能否用单手翅膀承接</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr" s="3">
+        <is>
+          <t>R09 R11</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr" s="3">
+        <is>
+          <t>Two Oruguitas</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr" s="3">
+        <is>
+          <t>查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" t="inlineStr" s="2">
+        <is>
+          <t>蝶-M005</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr" s="2">
+        <is>
+          <t>不论变化如何组织</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr" s="2">
+        <is>
+          <t>无论、不管与否定混在一句时</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr" s="2">
+        <is>
+          <t>批注提出不管方案，后续稿已在正文采用</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr" s="2">
+        <is>
+          <t>R03</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr" s="2">
+        <is>
+          <t>Two Oruguitas</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr" s="2">
+        <is>
+          <t>查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" t="inlineStr" s="3">
+        <is>
+          <t>蝶-M006</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr" s="3">
+        <is>
+          <t>奇迹围绕与等待奇迹</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr" s="3">
+        <is>
+          <t>重复副歌的相同英文对应了不同中文或转写时</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr" s="3">
+        <is>
+          <t>初稿的重复段差异与后续稿的统一；未写转写的末段不自动补齐</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr" s="3">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr" s="3">
+        <is>
+          <t>Two Oruguitas</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr" s="3">
+        <is>
+          <t>查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" t="inlineStr" s="2">
+        <is>
+          <t>蝶-M007</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr" s="2">
+        <is>
+          <t>结茧时的进与变成</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr" s="2">
+        <is>
+          <t>同一过程可以选身份变化或进入某个空间来表达时</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr" s="2">
+        <is>
+          <t>变成蛹与进蛹两种画面</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr" s="2">
+        <is>
+          <t>Two Oruguitas</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr" s="2">
+        <is>
+          <t>查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" t="inlineStr" s="3">
+        <is>
+          <t>蝶-M008</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr" s="3">
+        <is>
+          <t>茧的另一端与茧壳外面</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr" s="3">
+        <is>
+          <t>另一边、另一端需要判断是时间还是空间时</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr" s="3">
+        <is>
+          <t>依据前文对象明确空间指向</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr" s="3">
+        <is>
+          <t>R06 R11</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr" s="3">
+        <is>
+          <t>Two Oruguitas</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr" s="3">
+        <is>
+          <t>查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" t="inlineStr" s="2">
+        <is>
+          <t>蝶-M009</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr" s="2">
+        <is>
+          <t>两只毛毛虫与两个蛹</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr" s="2">
+        <is>
+          <t>两个主体进入下一状态，考虑如何继续区分主体时</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr" s="2">
+        <is>
+          <t>两手同时表达与主体数量</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr" s="2">
+        <is>
+          <t>R07 R09</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr" s="2">
+        <is>
+          <t>Two Oruguitas</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr" s="2">
+        <is>
+          <t>查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="42" customHeight="1">
+      <c r="A37" t="inlineStr" s="3">
+        <is>
+          <t>蝶-M010</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr" s="3">
+        <is>
+          <t>裂缝与裂开</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr" s="3">
+        <is>
+          <t>想描述物体破开时，在名词词条与动作画面之间选择时</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr" s="3">
+        <is>
+          <t>裂缝、裂开及参考图的边界</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr" s="3">
+        <is>
+          <t>R09 R10</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr" s="3">
+        <is>
+          <t>Two Oruguitas</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr" s="3">
+        <is>
+          <t>查看</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G2" r:id="link2"/>
@@ -734,6 +1474,26 @@
     <hyperlink ref="G15" r:id="link15"/>
     <hyperlink ref="G16" r:id="link16"/>
     <hyperlink ref="G17" r:id="link17"/>
+    <hyperlink ref="G18" r:id="link18"/>
+    <hyperlink ref="G19" r:id="link19"/>
+    <hyperlink ref="G20" r:id="link20"/>
+    <hyperlink ref="G21" r:id="link21"/>
+    <hyperlink ref="G22" r:id="link22"/>
+    <hyperlink ref="G23" r:id="link23"/>
+    <hyperlink ref="G24" r:id="link24"/>
+    <hyperlink ref="G25" r:id="link25"/>
+    <hyperlink ref="G26" r:id="link26"/>
+    <hyperlink ref="G27" r:id="link27"/>
+    <hyperlink ref="G28" r:id="link28"/>
+    <hyperlink ref="G29" r:id="link29"/>
+    <hyperlink ref="G30" r:id="link30"/>
+    <hyperlink ref="G31" r:id="link31"/>
+    <hyperlink ref="G32" r:id="link32"/>
+    <hyperlink ref="G33" r:id="link33"/>
+    <hyperlink ref="G34" r:id="link34"/>
+    <hyperlink ref="G35" r:id="link35"/>
+    <hyperlink ref="G36" r:id="link36"/>
+    <hyperlink ref="G37" r:id="link37"/>
   </hyperlinks>
   <tableParts count="1">
     <tablePart r:id="table1"/>
